--- a/merged.xlsx
+++ b/merged.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,17 +424,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>年龄</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>工资</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>性别</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>年龄</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>是否已婚</t>
         </is>
       </c>
     </row>
@@ -444,17 +449,20 @@
           <t>张三</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>男</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>23</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>是</t>
         </is>
       </c>
     </row>
@@ -464,19 +472,79 @@
           <t>李四</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>人力资源部</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
